--- a/Side Bar Files/GWD Data/Water Meter.xlsx
+++ b/Side Bar Files/GWD Data/Water Meter.xlsx
@@ -316,9 +316,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -742,7 +748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD18D2A4-EAFF-4D4B-A5EA-7DC49D3EB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029A2E31-BACD-4E97-8970-6CAC4EE8B9A7}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Water Meter.xlsx
+++ b/Side Bar Files/GWD Data/Water Meter.xlsx
@@ -9,7 +9,13 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -283,25 +289,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -367,11 +359,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -450,6 +442,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -748,7 +847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029A2E31-BACD-4E97-8970-6CAC4EE8B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1486D349-5C94-4C50-963C-ED074D71BAA6}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -865,6 +964,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="9">
+        <f t="array" ref="E8">IFERROR(INDEX(LMRRates,MATCH(B7,LMRCodes,0),),)</f>
         <v>875</v>
       </c>
       <c r="F8" s="9">
@@ -1263,6 +1363,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="9">
+        <f t="array" ref="E34">IFERROR(INDEX(LMRRates,MATCH(B33,LMRCodes,0),),)</f>
         <v>1228</v>
       </c>
       <c r="F34" s="9">

--- a/Side Bar Files/GWD Data/Water Meter.xlsx
+++ b/Side Bar Files/GWD Data/Water Meter.xlsx
@@ -847,7 +847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1486D349-5C94-4C50-963C-ED074D71BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F1567-CD3A-43CF-9A7C-C5F2BF04BAA6}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Water Meter.xlsx
+++ b/Side Bar Files/GWD Data/Water Meter.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -492,10 +492,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -847,7 +847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F1567-CD3A-43CF-9A7C-C5F2BF04BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F903535F-D1E8-445A-AFCD-395EC23BBAA6}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
